--- a/results/cp_comparison_summary.xlsx
+++ b/results/cp_comparison_summary.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main experiment" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reduced ant" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run details" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -487,7 +488,7 @@
         <v>0.076365</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009105</v>
+        <v>0.08705599999999999</v>
       </c>
       <c r="G5" t="n">
         <v>95.16200000000001</v>
@@ -512,7 +513,7 @@
         <v>0.086632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00586</v>
+        <v>0.107546</v>
       </c>
       <c r="G6" t="n">
         <v>49.48</v>
@@ -553,7 +554,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -581,7 +582,7 @@
         <v>0.250221</v>
       </c>
       <c r="F10" t="n">
-        <v>0.072007</v>
+        <v>0.985681</v>
       </c>
       <c r="G10" t="n">
         <v>53.716</v>
@@ -606,7 +607,7 @@
         <v>0.08641</v>
       </c>
       <c r="F11" t="n">
-        <v>0.017981</v>
+        <v>0.219767</v>
       </c>
       <c r="G11" t="n">
         <v>8.75</v>
@@ -647,7 +648,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -675,7 +676,7 @@
         <v>10.287576</v>
       </c>
       <c r="F15" t="n">
-        <v>1.586428</v>
+        <v>13.602579</v>
       </c>
       <c r="G15" t="n">
         <v>465.826</v>
@@ -700,7 +701,7 @@
         <v>6.139699</v>
       </c>
       <c r="F16" t="n">
-        <v>0.594859</v>
+        <v>8.749294000000001</v>
       </c>
       <c r="G16" t="n">
         <v>136.817</v>
@@ -762,7 +763,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -790,7 +791,7 @@
         <v>0.076365</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009105</v>
+        <v>0.08705599999999999</v>
       </c>
       <c r="G5" t="n">
         <v>95.16200000000001</v>
@@ -815,7 +816,7 @@
         <v>0.08010399999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00679</v>
+        <v>0.095012</v>
       </c>
       <c r="G6" t="n">
         <v>110.2</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -884,7 +885,7 @@
         <v>0.250221</v>
       </c>
       <c r="F10" t="n">
-        <v>0.072007</v>
+        <v>0.985681</v>
       </c>
       <c r="G10" t="n">
         <v>53.716</v>
@@ -909,7 +910,7 @@
         <v>0.109843</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0286</v>
+        <v>0.285993</v>
       </c>
       <c r="G11" t="n">
         <v>27.328</v>
@@ -950,7 +951,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Time std (s)</t>
+          <t>Time std mean (s)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,7 +979,7 @@
         <v>10.287576</v>
       </c>
       <c r="F15" t="n">
-        <v>1.586428</v>
+        <v>13.602579</v>
       </c>
       <c r="G15" t="n">
         <v>465.826</v>
@@ -1003,10 +1004,1973 @@
         <v>7.929927</v>
       </c>
       <c r="F16" t="n">
-        <v>1.29421</v>
+        <v>12.693767</v>
       </c>
       <c r="G16" t="n">
         <v>427.478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Per-run metrics (from each run CSV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Puzzle size</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Complete coverage</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Success % (run mean)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Time mean (run mean, s)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Time std (run std of instance means, s)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cycles mean (run mean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.070663</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08418299999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07226200000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08393100000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>89.66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.071992</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.057463</v>
+      </c>
+      <c r="J6" t="n">
+        <v>90.77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.092471</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.120055</v>
+      </c>
+      <c r="J7" t="n">
+        <v>118.37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.07443900000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08965099999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>93.01000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.08057400000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.083449</v>
+      </c>
+      <c r="J9" t="n">
+        <v>45.06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.08905399999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.123342</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.08748400000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.120311</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50.44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.08130900000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.090825</v>
+      </c>
+      <c r="J12" t="n">
+        <v>46.57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.094738</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.119804</v>
+      </c>
+      <c r="J13" t="n">
+        <v>54.51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.082924</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.112113</v>
+      </c>
+      <c r="J14" t="n">
+        <v>114.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.071145</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.078387</v>
+      </c>
+      <c r="J15" t="n">
+        <v>97.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.08411200000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.079485</v>
+      </c>
+      <c r="J16" t="n">
+        <v>115.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08741</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.116567</v>
+      </c>
+      <c r="J17" t="n">
+        <v>121.28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.07493</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.088506</v>
+      </c>
+      <c r="J18" t="n">
+        <v>102.61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>99</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.179047</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.350198</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38.768</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.235311</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.473018</v>
+      </c>
+      <c r="J20" t="n">
+        <v>48.42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.346413</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.537715</v>
+      </c>
+      <c r="J21" t="n">
+        <v>74.06</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.189721</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.712021</v>
+      </c>
+      <c r="J22" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.855452</v>
+      </c>
+      <c r="J23" t="n">
+        <v>65.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.082319</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.158415</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.072362</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.147647</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.115173</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.467351</v>
+      </c>
+      <c r="J26" t="n">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09098100000000001</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.186694</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.071213</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.138729</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.153178</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.56673</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.120657</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.264842</v>
+      </c>
+      <c r="J30" t="n">
+        <v>29.68</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.095175</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.255308</v>
+      </c>
+      <c r="J31" t="n">
+        <v>24.01</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.07822</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.139301</v>
+      </c>
+      <c r="J32" t="n">
+        <v>19.33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16x16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.101984</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.203784</v>
+      </c>
+      <c r="J33" t="n">
+        <v>25.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>81</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9.348807000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.983677</v>
+      </c>
+      <c r="J34" t="n">
+        <v>428.605</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>84</v>
+      </c>
+      <c r="H35" t="n">
+        <v>9.227693</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.827549</v>
+      </c>
+      <c r="J35" t="n">
+        <v>411.083</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10.498913</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11.910051</v>
+      </c>
+      <c r="J36" t="n">
+        <v>465.125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>86</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12.972947</v>
+      </c>
+      <c r="I37" t="n">
+        <v>19.7771</v>
+      </c>
+      <c r="J37" t="n">
+        <v>590.5119999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CP-ACS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>82</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9.389521</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14.514517</v>
+      </c>
+      <c r="J38" t="n">
+        <v>433.805</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>99</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.206013</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10.104015</v>
+      </c>
+      <c r="J39" t="n">
+        <v>142.434</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.287704</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.87433</v>
+      </c>
+      <c r="J40" t="n">
+        <v>140.06</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>99</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5.312428</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6.681543</v>
+      </c>
+      <c r="J41" t="n">
+        <v>116.172</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.954552</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10.729438</v>
+      </c>
+      <c r="J42" t="n">
+        <v>155.42</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>main experiment</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>99</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5.937799</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6.357143</v>
+      </c>
+      <c r="J43" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>96</v>
+      </c>
+      <c r="H44" t="n">
+        <v>8.042329000000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.945861</v>
+      </c>
+      <c r="J44" t="n">
+        <v>418.562</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>99</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8.177025</v>
+      </c>
+      <c r="I45" t="n">
+        <v>14.141171</v>
+      </c>
+      <c r="J45" t="n">
+        <v>425.576</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>99</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7.905285</v>
+      </c>
+      <c r="I46" t="n">
+        <v>13.488334</v>
+      </c>
+      <c r="J46" t="n">
+        <v>427.697</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9.574894</v>
+      </c>
+      <c r="I47" t="n">
+        <v>15.108942</v>
+      </c>
+      <c r="J47" t="n">
+        <v>529.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>reduced ant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>25x25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CP-DCM-ACO (9 ants)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>98</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.950102</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6.784525</v>
+      </c>
+      <c r="J48" t="n">
+        <v>336.153</v>
       </c>
     </row>
   </sheetData>
